--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-procedure.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-procedure.xlsx
@@ -364,7 +364,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -500,7 +500,7 @@
     <t>Procedure.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|ActivityDefinition|Measure|OperationDefinition|Questionnaire)
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1|Questionnaire|4.0.1)
 </t>
   </si>
   <si>
@@ -538,7 +538,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1434,7 +1434,7 @@
     <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -1595,7 +1595,7 @@
     <t>Procedure.focalDevice.manipulated</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device)
+    <t xml:space="preserve">Reference(Device|4.0.1)
 </t>
   </si>
   <si>
